--- a/xls/square_16_tri3_16.xlsx
+++ b/xls/square_16_tri3_16.xlsx
@@ -482,13 +482,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>0.7040235020566389</v>
+        <v>0.7040234163707318</v>
       </c>
       <c r="J16">
-        <v>-1.912290547837643</v>
+        <v>-1.9122906929738215</v>
       </c>
       <c r="K16">
-        <v>-0.5299044334855166</v>
+        <v>-0.5299043989129579</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-2.4571098312728363</v>
+        <v>-2.4571102997828373</v>
       </c>
       <c r="J17">
-        <v>-2.1104205949732173</v>
+        <v>-2.1104207075033448</v>
       </c>
       <c r="K17">
-        <v>-0.1854570258727821</v>
+        <v>-0.18533336826900698</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-1.9605730521424856</v>
+        <v>-1.960572081664392</v>
       </c>
       <c r="J18">
-        <v>-1.503158405910744</v>
+        <v>-1.5031581727949483</v>
       </c>
       <c r="K18">
-        <v>2.9234205357209135</v>
+        <v>2.923420515934336</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.8686750122942146</v>
+        <v>-0.8686750034927418</v>
       </c>
       <c r="J19">
-        <v>-0.7288500363909719</v>
+        <v>-0.7288500228141475</v>
       </c>
       <c r="K19">
-        <v>3.609346524388788</v>
+        <v>3.6093465136653022</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-1.6141166641826696</v>
+        <v>-1.6141164705090219</v>
       </c>
       <c r="J20">
-        <v>-1.2929513167166387</v>
+        <v>-1.2929512452874765</v>
       </c>
       <c r="K20">
-        <v>3.418524357742033</v>
+        <v>3.4185243603346405</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.49968332516178077</v>
+        <v>-0.49968335696889554</v>
       </c>
       <c r="J21">
-        <v>-0.5011360710665212</v>
+        <v>-0.5011360952349738</v>
       </c>
       <c r="K21">
-        <v>3.837807481342605</v>
+        <v>3.8378074888112788</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.30244754087639036</v>
+        <v>-0.302447544974608</v>
       </c>
       <c r="J22">
-        <v>-0.3036552783562427</v>
+        <v>-0.3036552800529197</v>
       </c>
       <c r="K22">
-        <v>3.949527735611608</v>
+        <v>3.9495277357532217</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.09855314624921234</v>
+        <v>-0.09855314549841748</v>
       </c>
       <c r="J23">
-        <v>-0.09929738441679019</v>
+        <v>-0.09929738392515497</v>
       </c>
       <c r="K23">
-        <v>3.8673196078037355</v>
+        <v>3.8673196068438362</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.11583665930441696</v>
+        <v>-0.1158366588824233</v>
       </c>
       <c r="J24">
-        <v>-0.1121778797646714</v>
+        <v>-0.11217787950290603</v>
       </c>
       <c r="K24">
-        <v>3.883880659082406</v>
+        <v>3.8838806579571523</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -797,13 +797,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.02049110518721723</v>
+        <v>-0.02049110533706566</v>
       </c>
       <c r="J25">
-        <v>-0.021587650701222056</v>
+        <v>-0.021587650776878676</v>
       </c>
       <c r="K25">
-        <v>3.6056025775658314</v>
+        <v>3.605602577559387</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.012047772160007257</v>
+        <v>-0.012047772177374993</v>
       </c>
       <c r="J26">
-        <v>-0.013007081484671706</v>
+        <v>-0.013007081487464895</v>
       </c>
       <c r="K26">
-        <v>3.5081168351893792</v>
+        <v>3.5081168349771183</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -867,13 +867,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.008133290741049343</v>
+        <v>-0.008133290775642331</v>
       </c>
       <c r="J27">
-        <v>-0.008857438329328513</v>
+        <v>-0.008857438352088508</v>
       </c>
       <c r="K27">
-        <v>3.427599256270348</v>
+        <v>3.4275992569632576</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -902,13 +902,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.00630989921352449</v>
+        <v>-0.006309899215281328</v>
       </c>
       <c r="J28">
-        <v>-0.006545962329681379</v>
+        <v>-0.0065459623313984475</v>
       </c>
       <c r="K28">
-        <v>3.3529405024245253</v>
+        <v>3.3529405025113355</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.005491171350353871</v>
+        <v>-0.00549117135265703</v>
       </c>
       <c r="J29">
-        <v>-0.004639972759637236</v>
+        <v>-0.004639972759887877</v>
       </c>
       <c r="K29">
-        <v>3.248791630104844</v>
+        <v>3.2487916297941593</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -972,13 +972,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.00629832749965595</v>
+        <v>-0.006298327502491297</v>
       </c>
       <c r="J30">
-        <v>-0.006047405488528808</v>
+        <v>-0.006047405490294511</v>
       </c>
       <c r="K30">
-        <v>3.3292741698716304</v>
+        <v>3.329274169989718</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>0.00022773038093511263</v>
+        <v>0.00022773038089742717</v>
       </c>
       <c r="J31">
-        <v>6.139885589265894e-5</v>
+        <v>6.139885588301702e-5</v>
       </c>
       <c r="K31">
-        <v>2.4973327541392005</v>
+        <v>2.4973327541942867</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.00038337025663342145</v>
+        <v>-0.0003833702568917999</v>
       </c>
       <c r="J32">
-        <v>-0.00022332582062331214</v>
+        <v>-0.0002233258207733904</v>
       </c>
       <c r="K32">
-        <v>2.2168514955322345</v>
+        <v>2.216851495963395</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_16.xlsx
+++ b/xls/square_16_tri3_16.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>289</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>289</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1176</v>
+      </c>
+      <c r="I14">
+        <v>3.3133275056889584</v>
+      </c>
+      <c r="J14">
+        <v>-0.05103964673358577</v>
+      </c>
+      <c r="K14">
+        <v>1.0046599022316096</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>289</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>289</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1350</v>
+      </c>
+      <c r="I15">
+        <v>2.2198131394891227</v>
+      </c>
+      <c r="J15">
+        <v>-0.8310865049197954</v>
+      </c>
+      <c r="K15">
+        <v>0.4751718557415726</v>
+      </c>
+    </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>11</v>
